--- a/data/credit_bond_all_2026-09-16.xlsx
+++ b/data/credit_bond_all_2026-09-16.xlsx
@@ -780,7 +780,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>3.95</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
@@ -924,7 +926,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26上海农商绿色债01B</t>
+          <t>26上海农商绿色债02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -932,7 +934,11 @@
           <t>09-16 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2621006.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -941,14 +947,20 @@
       <c r="E4" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.35 ~ 1.85</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>35.03</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1177,8 +1189,12 @@
           <t>1.34 ~ 1.49</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>29.66</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -1405,8 +1421,12 @@
           <t>1.29 ~ 1.49</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>15.65</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -1637,8 +1657,12 @@
           <t>1.25 ~ 1.65</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>15.71</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -1867,8 +1891,12 @@
           <t>1.30 ~ 1.80</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>22.06</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.54</t>
@@ -2099,8 +2127,12 @@
           <t>1.95 ~ 2.95</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>117.97</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>2.72</t>
@@ -2331,8 +2363,12 @@
           <t>1.30 ~ 1.55</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>17.98</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -2789,8 +2825,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>35.97</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -2850,7 +2890,7 @@
         <v>6.85</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>6.46</v>
+        <v>6.47</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -3021,8 +3061,12 @@
           <t>1.10 ~ 2.10</t>
         </is>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>35.03</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -3251,8 +3295,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>26.97</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>1.82</t>
@@ -3703,8 +3751,12 @@
           <t>1.90 ~ 2.50</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>87.61</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>2.14</t>
@@ -3761,7 +3813,7 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>1.6</v>
@@ -3939,8 +3991,12 @@
           <t>1.80 ~ 2.30</t>
         </is>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>109.06</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>2.20</t>
@@ -4167,8 +4223,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>20.06</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>1.56</t>
@@ -4401,8 +4461,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>17.98</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -4459,7 +4523,7 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.76</v>
+        <v>2.755</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>1.05</v>
@@ -4631,8 +4695,12 @@
           <t>1.20 ~ 1.55</t>
         </is>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>14.26</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>1.51</t>
@@ -4861,8 +4929,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>46.03</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -5319,8 +5391,12 @@
           <t>1.50 ~ 2.10</t>
         </is>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>45.03</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -5805,7 +5881,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.7600</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5982,7 +6058,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26中铁十一MTN004A</t>
+          <t>26中铁十一MTN004A(取消发行)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5992,7 +6068,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683680.IB</t>
+          <t>DY102683680.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6003,9 +6079,7 @@
       <c r="E26" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.20</t>
@@ -6068,12 +6142,8 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>2.86</v>
-      </c>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -6123,7 +6193,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司2026年度第四期中期票据(品种一)</t>
+          <t>中铁十一局集团有限公司2026年度第四期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6194,7 +6264,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6243,8 +6313,12 @@
           <t>1.29 ~ 1.49</t>
         </is>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="H27" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>14.0</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -6990,7 +7064,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>2.92</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -7607,8 +7683,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="H33" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>21.42</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>1.92</t>
@@ -7898,7 +7978,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
@@ -8820,7 +8902,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>6.14</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
@@ -9048,7 +9132,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>6.25</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
@@ -9724,7 +9810,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U42" s="3"/>
+      <c r="U42" s="4" t="n">
+        <v>4.33</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
@@ -10836,7 +10924,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4" t="n">
+        <v>3.44</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
@@ -11911,8 +12001,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+      <c r="H52" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>42.97</v>
+      </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -12428,7 +12522,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U54" s="3"/>
+      <c r="U54" s="4" t="n">
+        <v>4.47</v>
+      </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
@@ -13054,15 +13150,19 @@
         <v>5.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+      <c r="H57" s="4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>65.97</v>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -14500,7 +14600,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U63" s="3"/>
+      <c r="U63" s="4" t="n">
+        <v>3.97</v>
+      </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
@@ -15776,7 +15878,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26上海农商绿色债01A</t>
+          <t>26北京银行永续债02</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -15787,53 +15889,57 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>30.0</v>
+        <v>200.0</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+          <t>1.70 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>46.97</v>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>25上海农商绿色债01(柜台)</t>
+          <t>26北京银行永续债01</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>1.81Y</t>
+          <t>4.70Y+N</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.5011</t>
+          <t>1.8731</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8650/1.8550</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司</t>
+          <t>北京银行股份有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>A 71.80</t>
+          <t>S- 85.00</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -15856,16 +15962,18 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U69" s="3"/>
+      <c r="U69" s="4" t="n">
+        <v>2.6</v>
+      </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.61%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -15880,23 +15988,23 @@
       </c>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。 </t>
+          <t>本期债券的募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海浦东发展银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,招商证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -15911,7 +16019,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司2026年绿色金融债券(第一期)(品种一)</t>
+          <t>北京银行股份有限公司2026年无固定期限资本债券(第二期)</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -15921,7 +16029,7 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
@@ -15962,7 +16070,7 @@
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
@@ -15982,12 +16090,12 @@
       </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX69" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY69" s="3" t="inlineStr">
@@ -16000,64 +16108,74 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26北京银行永续债02</t>
+          <t>26温州银行债01B</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
-        </is>
-      </c>
-      <c r="C70" s="3"/>
+          <t>09-16 16:30</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>212680046.IB</t>
+        </is>
+      </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>44.03</v>
+      </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26北京银行永续债01</t>
+          <t>25温州银行债03A</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>4.70Y+N</t>
+          <t>2.20Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.8731</t>
+          <t>1.6236</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>1.8650/1.8550</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司</t>
+          <t>温州银行股份有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>S- 85.00</t>
+          <t>C+ 33.60</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16080,18 +16198,16 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U70" s="4" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="U70" s="3"/>
       <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16106,23 +16222,23 @@
       </c>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
+          <t xml:space="preserve">本期债券的募集资金将依据适用法律和主管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。 </t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,招商证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信建投证券股份有限公司,华夏银行股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16137,7 +16253,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司2026年无固定期限资本债券(第二期)</t>
+          <t>温州银行股份有限公司2026年金融债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16147,7 +16263,7 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK70" s="3"/>
@@ -16173,7 +16289,7 @@
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
@@ -16208,12 +16324,12 @@
       </c>
       <c r="AW70" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX70" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY70" s="3" t="inlineStr">
@@ -16226,106 +16342,110 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26温州银行债01B</t>
+          <t>26中兴通讯SCP038</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>09-16 16:30</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>212680046.IB</t>
+          <t>012682274.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.29Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>1.25 ~ 1.65</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>26中兴通讯MTN001</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>2.41Y</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>1.7064</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>中兴通讯股份有限公司</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.14</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>09-16 09:00</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V71" s="4" t="n">
         <v>1.0</v>
       </c>
-      <c r="F71" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>25温州银行债03A</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>2.20Y</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>1.6236</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>温州银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.60</t>
-        </is>
-      </c>
-      <c r="Q71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="R71" s="3" t="inlineStr">
-        <is>
-          <t>09-16 09:00</t>
-        </is>
-      </c>
-      <c r="S71" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -16333,35 +16453,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z71" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券的募集资金将依据适用法律和主管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。 </t>
+          <t>本期超短期融资券拟募集资金6亿元，资金将全部用于偿还发行人即将到期的债务融资工具本息。[26中兴通讯SCP026]</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华夏银行股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG71" s="3" t="inlineStr">
@@ -16371,7 +16487,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>温州银行股份有限公司2026年金融债券(第一期)(品种二)</t>
+          <t>中兴通讯股份有限公司2026年度第三十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16381,60 +16497,60 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr">
+        <is>
+          <t>电子设备制造</t>
+        </is>
+      </c>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>通信设备</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>通信设备</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>通信设备</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AO71" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ71" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR71" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS71" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT71" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV71" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -16455,12 +16571,14 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ71" s="3"/>
+      <c r="AZ71" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26中兴通讯SCP038</t>
+          <t>26中兴通讯SCP036</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16470,7 +16588,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>012682274.IB</t>
+          <t>012682282.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -16479,18 +16597,22 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
           <t>1.25 ~ 1.65</t>
         </is>
       </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="H72" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>15.71</v>
+      </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -16533,7 +16655,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 14:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16547,7 +16669,7 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="V72" s="4" t="n">
         <v>1.0</v>
@@ -16575,12 +16697,12 @@
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金6亿元，资金将全部用于偿还发行人即将到期的债务融资工具本息。[26中兴通讯SCP026]</t>
+          <t>本期超短期融资券募集资金为8亿元，拟用于偿还发行人即将到期的债务融资工具[26中兴通讯SCP024]</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
@@ -16601,7 +16723,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>中兴通讯股份有限公司2026年度第三十八期超短期融资券</t>
+          <t>中兴通讯股份有限公司2026年度第三十六期超短期融资券</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16685,14 +16807,12 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ72" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ72" s="3"/>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26中兴通讯SCP036</t>
+          <t>26芯鑫租赁MTN002</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -16702,45 +16822,49 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>012682282.IB</t>
+          <t>102683676.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>0.29Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.65</t>
-        </is>
-      </c>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+          <t>1.50 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>40.61</v>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>26中兴通讯MTN001</t>
+          <t>26芯鑫租赁MTN001</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2.41Y</t>
+          <t>2.60Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.7064</t>
+          <t>1.7210</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -16750,12 +16874,12 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>中兴通讯股份有限公司</t>
+          <t>芯鑫融资租赁集团股份有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 35.14</t>
+          <t>D+ 9.30</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -16765,7 +16889,7 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>09-16 14:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -16779,19 +16903,19 @@
         </is>
       </c>
       <c r="U73" s="4" t="n">
-        <v>2.46</v>
+        <v>1.62</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>1.0</v>
+        <v>1.02</v>
       </c>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
@@ -16799,31 +16923,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z73" s="3"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金为8亿元，拟用于偿还发行人即将到期的债务融资工具[26中兴通讯SCP024]</t>
+          <t>本期债务融资工具10亿元,拟用于归还发行人及子公司银行借款。</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
+          <t>上海银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG73" s="3" t="inlineStr">
@@ -16833,7 +16961,7 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>中兴通讯股份有限公司2026年度第三十六期超短期融资券</t>
+          <t>芯鑫融资租赁集团股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -16843,10 +16971,14 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="AK73" s="3"/>
+          <t>2028-09-17</t>
+        </is>
+      </c>
+      <c r="AK73" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL73" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -16864,32 +16996,32 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -16917,75 +17049,81 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ73" s="3"/>
+      <c r="AZ73" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26新业国资MTN003</t>
+          <t>26国电CP009</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>102683691.IB</t>
+          <t>042680316.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
+          <t>1.30 ~ 1.55</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>17.98</v>
+      </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>26新业国资MTN001</t>
+          <t>24国电MTN003</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>1.01Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>2.1552</t>
+          <t>1.5208</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.5100</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>新疆新业国有资产经营(集团)有限责任公司</t>
+          <t>国电电力发展股份有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C- 14.72</t>
+          <t>B- 47.08</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -16995,7 +17133,7 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>09-16 10:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -17005,51 +17143,55 @@
       </c>
       <c r="T74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>辽宁省-大连市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据注册金额20亿元,本期发行规模5亿元,拟全部用于偿还有息负债[23新业国资MTN002]</t>
+          <t xml:space="preserve">经交易商协会注册，发行人将于注册有效期内根据发行计划发行债务融资工具。本期债务融资工具发行金额25亿元，募集资金拟用于偿还到期债务及补充流动资金。 </t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
+          <t>浙商银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
       <c r="AE74" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF74" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG74" s="3" t="inlineStr">
@@ -17059,7 +17201,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>新疆新业国有资产经营(集团)有限责任公司2026年度第三期中期票据</t>
+          <t>国电电力发展股份有限公司2026年度第九期短期融资券</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17069,13 +17211,13 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM74" s="3" t="inlineStr">
@@ -17085,7 +17227,7 @@
       </c>
       <c r="AN74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AO74" s="3" t="inlineStr">
@@ -17095,22 +17237,22 @@
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
@@ -17140,17 +17282,15 @@
       </c>
       <c r="AY74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AZ74" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AZ74" s="3"/>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26芯鑫租赁MTN002</t>
+          <t>26中交建筑SCP004</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -17160,60 +17300,60 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>102683676.IB</t>
+          <t>012682270.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.70</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26芯鑫租赁MTN001</t>
+          <t>26中交建筑SCP003</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2.60Y</t>
+          <t>99D</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.7210</t>
+          <t>1.5004</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4900</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>芯鑫融资租赁集团股份有限公司</t>
+          <t>中交建筑集团有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.30</t>
+          <t>C 26.48</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17236,20 +17376,16 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U75" s="4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>1.02</v>
-      </c>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -17257,35 +17393,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z75" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具10亿元,拟用于归还发行人及子公司银行借款。</t>
+          <t>发行人本期超短融资券发行规模为人民币20亿元,发行人拟将本次发行所募集的资金用于偿还发行人到期有息债务。[26中交建筑SCP001]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,南京银行股份有限公司</t>
+          <t>渤海银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
@@ -17295,7 +17427,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>芯鑫融资租赁集团股份有限公司2026年度第二期中期票据</t>
+          <t>中交建筑集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17305,14 +17437,10 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2028-09-17</t>
-        </is>
-      </c>
-      <c r="AK75" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-03-16</t>
+        </is>
+      </c>
+      <c r="AK75" s="3"/>
       <c r="AL75" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -17330,32 +17458,32 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17384,13 +17512,13 @@
         </is>
       </c>
       <c r="AZ75" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26国电CP009</t>
+          <t>26广核电力MTN008</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17400,60 +17528,64 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>042680316.IB</t>
+          <t>102683674.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.55</t>
-        </is>
-      </c>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>27.97</v>
+      </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>24国电MTN003</t>
+          <t>26广核电力MTN006</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>1.01Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.5208</t>
+          <t>1.7270</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.5100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>国电电力发展股份有限公司</t>
+          <t>中国广核电力股份有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>B- 47.08</t>
+          <t>C- 15.73</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17477,11 +17609,9 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.56</v>
+      </c>
+      <c r="V76" s="3"/>
       <c r="W76" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -17489,7 +17619,7 @@
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -17500,23 +17630,23 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-大连市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">经交易商协会注册，发行人将于注册有效期内根据发行计划发行债务融资工具。本期债务融资工具发行金额25亿元，募集资金拟用于偿还到期债务及补充流动资金。 </t>
+          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司到期贷款本息。</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国建设银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>招商银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF76" s="3" t="inlineStr">
@@ -17531,7 +17661,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>国电电力发展股份有限公司2026年度第九期短期融资券</t>
+          <t>中国广核电力股份有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17541,7 +17671,7 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AK76" s="3"/>
@@ -17567,7 +17697,7 @@
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
@@ -17582,7 +17712,7 @@
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
@@ -17620,7 +17750,7 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26中交建筑SCP004</t>
+          <t>26涪陵实业MTN002A(取消发行)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -17630,60 +17760,58 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>012682270.IB</t>
+          <t>DY102683682.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>26中交建筑SCP003</t>
+          <t>26涪陵实业MTN001</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>99D</t>
+          <t>6.75Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1.5004</t>
+          <t>2.2223</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>--/1.4900</t>
+          <t>--/2.1600</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>中交建筑集团有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C 26.48</t>
+          <t>C- 16.85</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -17693,7 +17821,7 @@
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 14:00</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr">
@@ -17715,39 +17843,39 @@
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短融资券发行规模为人民币20亿元,发行人拟将本次发行所募集的资金用于偿还发行人到期有息债务。[26中交建筑SCP001]</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为4.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
       <c r="AE77" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF77" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG77" s="3" t="inlineStr">
@@ -17757,7 +17885,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>中交建筑集团有限公司2026年度第四期超短期融资券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -17767,10 +17895,14 @@
       </c>
       <c r="AJ77" s="3" t="inlineStr">
         <is>
-          <t>2027-03-16</t>
-        </is>
-      </c>
-      <c r="AK77" s="3"/>
+          <t>2033-09-17</t>
+        </is>
+      </c>
+      <c r="AK77" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL77" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -17788,32 +17920,32 @@
       </c>
       <c r="AO77" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -17841,14 +17973,12 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ77" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ77" s="3"/>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN008</t>
+          <t>26连云港SCP003</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -17858,60 +17988,64 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>102683674.IB</t>
+          <t>012682277.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>36.06</v>
+      </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN006</t>
+          <t>26连云港SCP002</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>96D</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.7270</t>
+          <t>1.5543</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C- 15.73</t>
+          <t>C- 20.60</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -17935,49 +18069,49 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>2.56</v>
+        <v>3.93</v>
       </c>
       <c r="V78" s="3"/>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.58%~1.62%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司到期贷款本息。</t>
+          <t>本期债务融资工具发行金额3亿元,用于偿还发行人有息债务本息</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,平安银行股份有限公司</t>
+          <t>招商银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
       <c r="AE78" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF78" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG78" s="3" t="inlineStr">
@@ -17987,7 +18121,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司2026年度第八期中期票据</t>
+          <t>连云港港口集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -17997,7 +18131,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2027-06-14</t>
         </is>
       </c>
       <c r="AK78" s="3"/>
@@ -18023,27 +18157,27 @@
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT78" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU78" s="3" t="inlineStr">
@@ -18071,12 +18205,14 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ78" s="3"/>
+      <c r="AZ78" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002A</t>
+          <t>26潞安MTN007A</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18086,60 +18222,64 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>102683682.IB</t>
+          <t>102683661.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2.1</v>
+        <v>3.0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2.1</v>
+        <v>3.0</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>51.03</v>
+      </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>26潞安MTN006A</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>6.75Y</t>
+          <t>2.94Y+N</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>2.2223</t>
+          <t>1.7684</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>--/2.1600</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>山西潞安矿业(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C- 16.85</t>
+          <t>B- 39.15</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18149,7 +18289,7 @@
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>09-16 14:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -18163,40 +18303,40 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>4.24</v>
+        <v>4.37</v>
       </c>
       <c r="V79" s="4" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>山西省-长治市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为4.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币10亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
@@ -18217,7 +18357,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第二期中期票据(品种一)</t>
+          <t>山西潞安矿业(集团)有限责任公司2026年度第七期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18227,14 +18367,10 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2033-09-17</t>
-        </is>
-      </c>
-      <c r="AK79" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-17</t>
+        </is>
+      </c>
+      <c r="AK79" s="3"/>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -18252,32 +18388,32 @@
       </c>
       <c r="AO79" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18292,7 +18428,7 @@
       </c>
       <c r="AW79" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX79" s="3" t="inlineStr">
@@ -18310,7 +18446,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP003</t>
+          <t>26潞安MTN007B</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18320,60 +18456,64 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>012682277.IB</t>
+          <t>102683662.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+          <t>1.70 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>60.97</v>
+      </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26连云港SCP002</t>
+          <t>26潞安MTN006B</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>96D</t>
+          <t>4.94Y+N</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.5543</t>
+          <t>2.0270</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>山西潞安矿业(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C- 20.60</t>
+          <t>B- 39.15</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18397,44 +18537,46 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="V80" s="3"/>
+        <v>2.36</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.62%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>山西省-长治市</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额3亿元,用于偿还发行人有息债务本息</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币10亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,交通银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
       <c r="AE80" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF80" s="3" t="inlineStr">
@@ -18449,7 +18591,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年度第三期超短期融资券</t>
+          <t>山西潞安矿业(集团)有限责任公司2026年度第七期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18459,7 +18601,7 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2027-06-14</t>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AK80" s="3"/>
@@ -18485,27 +18627,27 @@
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18520,7 +18662,7 @@
       </c>
       <c r="AW80" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX80" s="3" t="inlineStr">
@@ -18533,14 +18675,12 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ80" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ80" s="3"/>
     </row>
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN007A</t>
+          <t>26中飞租赁MTN001</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18550,60 +18690,64 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>102683661.IB</t>
+          <t>102683672.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>51.61</v>
+      </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN006A</t>
+          <t>25中飞租赁MTN002</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>2.94Y+N</t>
+          <t>1.24Y+N</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.7684</t>
+          <t>1.7289</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>1.9000/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司</t>
+          <t>中飞租融资租赁有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>B- 39.15</t>
+          <t>B- 37.87</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18613,7 +18757,7 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -18627,19 +18771,19 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>4.37</v>
+        <v>2.98</v>
       </c>
       <c r="V81" s="4" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -18650,17 +18794,17 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>山西省-长治市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币10亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
+          <t>本期债券募集资金用于归还发行人的待偿还公司债务[24中飞租赁MTN002]</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
@@ -18671,7 +18815,7 @@
       </c>
       <c r="AF81" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG81" s="3" t="inlineStr">
@@ -18681,7 +18825,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司2026年度第七期中期票据(品种一)</t>
+          <t>中飞租融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -18691,10 +18835,14 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
-        </is>
-      </c>
-      <c r="AK81" s="3"/>
+          <t>2028-09-17</t>
+        </is>
+      </c>
+      <c r="AK81" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL81" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -18712,32 +18860,32 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -18757,7 +18905,7 @@
       </c>
       <c r="AX81" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY81" s="3" t="inlineStr">
@@ -18765,12 +18913,14 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ81" s="3"/>
+      <c r="AZ81" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN007B</t>
+          <t>26冀建投MTN003</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -18780,60 +18930,64 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>102683662.IB</t>
+          <t>102683679.IB</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+          <t>1.50 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>33.03</v>
+      </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>26潞安MTN006B</t>
+          <t>26冀建投MTN002A</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>4.94Y+N</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>2.0270</t>
+          <t>1.6523</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司</t>
+          <t>河北建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>B- 39.15</t>
+          <t>C- 15.27</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -18857,19 +19011,19 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="V82" s="4" t="n">
-        <v>5.0</v>
+        <v>3.2</v>
       </c>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
@@ -18877,20 +19031,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z82" s="3"/>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>山西省-长治市</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币10亿元，募集资金拟用于偿还发行人或下属子公司的有息负债。</t>
+          <t>本期中期票据发行规模人民币8亿元，募集资金拟用于偿还发行人有息债务，补充发行人日常运营周转。</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
@@ -18911,7 +19069,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>山西潞安矿业(集团)有限责任公司2026年度第七期中期票据(品种二)</t>
+          <t>河北建设投资集团有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -18921,7 +19079,7 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2029-09-17</t>
         </is>
       </c>
       <c r="AK82" s="3"/>
@@ -18942,7 +19100,7 @@
       </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP82" s="3" t="inlineStr">
@@ -18952,22 +19110,22 @@
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -18982,7 +19140,7 @@
       </c>
       <c r="AW82" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX82" s="3" t="inlineStr">
@@ -19000,70 +19158,70 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26中飞租赁MTN001</t>
+          <t>26鲁黄金MTN001A</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>102683672.IB</t>
+          <t>102683688.IB</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>2.00 ~ 2.50</t>
         </is>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>25中飞租赁MTN002</t>
+          <t>25鲁黄金MTN006(科创债)</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>1.24Y+N</t>
+          <t>8.89Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.7289</t>
+          <t>2.0694</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.9000/--</t>
+          <t>--/1.9900</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>中飞租融资租赁有限公司</t>
+          <t>山东黄金集团有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>B- 37.87</t>
+          <t>C- 19.92</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19073,7 +19231,7 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -19083,23 +19241,19 @@
       </c>
       <c r="T83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U83" s="4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V83" s="4" t="n">
-        <v>1.45</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>2.29%~2.39%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -19107,20 +19261,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z83" s="3"/>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金用于归还发行人的待偿还公司债务[24中飞租赁MTN002]</t>
+          <t>本期中期票据发行金额上限10亿元,募集资金全部用于偿还公司存量有息负债。</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>招商银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
@@ -19131,7 +19289,7 @@
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
@@ -19141,7 +19299,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>中飞租融资租赁有限公司2026年度第一期中期票据</t>
+          <t>山东黄金集团有限公司2026年度第一期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19151,92 +19309,88 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2028-09-17</t>
-        </is>
-      </c>
-      <c r="AK83" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2046-09-18</t>
+        </is>
+      </c>
+      <c r="AK83" s="3"/>
       <c r="AL83" s="3" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AM83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN83" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AM83" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN83" s="3" t="inlineStr">
+      <c r="AO83" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP83" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ83" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR83" s="3" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AS83" s="3" t="inlineStr">
+        <is>
+          <t>贵金属</t>
+        </is>
+      </c>
+      <c r="AT83" s="3" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="AU83" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV83" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW83" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX83" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY83" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AO83" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP83" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ83" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR83" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS83" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT83" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU83" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV83" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW83" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX83" s="3" t="inlineStr">
-        <is>
-          <t>次级债权</t>
-        </is>
-      </c>
-      <c r="AY83" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="AZ83" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26冀建投MTN003</t>
+          <t>26中冶MTN004</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19246,60 +19400,64 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>102683679.IB</t>
+          <t>102683663.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>51.03</v>
+      </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>26冀建投MTN002A</t>
+          <t>26中冶MTN002</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>2.95Y+N</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.6523</t>
+          <t>1.7514</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>1.7550/--</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>河北建设投资集团有限责任公司</t>
+          <t>中国冶金科工股份有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>C- 15.27</t>
+          <t>B- 43.29</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19323,10 +19481,10 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>3.4</v>
+        <v>4.49</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>3.2</v>
+        <v>31.71</v>
       </c>
       <c r="W84" s="3" t="inlineStr">
         <is>
@@ -19335,7 +19493,7 @@
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
@@ -19350,17 +19508,17 @@
       </c>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模人民币8亿元，募集资金拟用于偿还发行人有息债务，补充发行人日常运营周转。</t>
+          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19371,7 +19529,7 @@
       </c>
       <c r="AF84" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG84" s="3" t="inlineStr">
@@ -19381,7 +19539,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>河北建设投资集团有限责任公司2026年度第三期中期票据</t>
+          <t>中国冶金科工股份有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19412,32 +19570,32 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19452,12 +19610,12 @@
       </c>
       <c r="AW84" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX84" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY84" s="3" t="inlineStr">
@@ -19465,12 +19623,14 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ84" s="3"/>
+      <c r="AZ84" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26鲁黄金MTN001A</t>
+          <t>26鲁黄金MTN001B</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19480,12 +19640,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>102683688.IB</t>
+          <t>102683689.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
@@ -19496,7 +19656,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.50</t>
+          <t>2.20 ~ 2.70</t>
         </is>
       </c>
       <c r="H85" s="3"/>
@@ -19523,7 +19683,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9900</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -19565,7 +19725,7 @@
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>2.29%~2.39%</t>
+          <t>2.33%~2.43%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
@@ -19611,7 +19771,7 @@
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司2026年度第一期中期票据(品种一)</t>
+          <t>山东黄金集团有限公司2026年度第一期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19621,7 +19781,7 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2046-09-18</t>
+          <t>2056-09-18</t>
         </is>
       </c>
       <c r="AK85" s="3"/>
@@ -19702,7 +19862,7 @@
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN004</t>
+          <t>26望城经开MTN001</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -19712,60 +19872,64 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>102683663.IB</t>
+          <t>102683666.IB</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>20.0</v>
+        <v>6.6</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>20.0</v>
+        <v>6.6</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>22.97</v>
+      </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN002</t>
+          <t>25望城经开MTN001</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+N</t>
+          <t>3.87Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.7514</t>
+          <t>1.8219</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>1.7550/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司</t>
+          <t>望城经开区投资建设集团有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>B- 43.29</t>
+          <t>C- 19.39</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -19775,7 +19939,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -19789,44 +19953,40 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>4.49</v>
+        <v>5.17</v>
       </c>
       <c r="V86" s="4" t="n">
-        <v>31.71</v>
+        <v>1.4</v>
       </c>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z86" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
+          <t>本次注册中期票据金额25.00亿元,本期发行规模6.60亿元,募集资金拟全部用于偿还发行人本部存量债务融资工具本金[23望城经开MTN002]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD86" s="3"/>
@@ -19837,7 +19997,7 @@
       </c>
       <c r="AF86" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG86" s="3" t="inlineStr">
@@ -19847,7 +20007,7 @@
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司2026年度第四期中期票据</t>
+          <t>望城经开区投资建设集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
@@ -19857,7 +20017,7 @@
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AK86" s="3"/>
@@ -19878,37 +20038,37 @@
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-17</t>
         </is>
       </c>
       <c r="AV86" s="3" t="inlineStr">
@@ -19918,12 +20078,12 @@
       </c>
       <c r="AW86" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX86" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY86" s="3" t="inlineStr">
@@ -19931,62 +20091,62 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ86" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ86" s="3"/>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26鲁黄金MTN001B</t>
+          <t>26济工02</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>102683689.IB</t>
+          <t>284042.SH</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+          <t>2.80 ~ 3.80</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>183.97</v>
+      </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>25鲁黄金MTN006(科创债)</t>
+          <t>24济工03</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>8.89Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>2.0694</t>
+          <t>2.8685</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -19996,12 +20156,12 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司</t>
+          <t>济南建工集团有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 19.92</t>
+          <t>C- 16.62</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20011,7 +20171,7 @@
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -20028,24 +20188,20 @@
       <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>2.33%~2.43%</t>
+          <t>3.50%~3.60%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z87" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
           <t>山东省-济南市</t>
@@ -20053,18 +20209,18 @@
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额上限10亿元,募集资金全部用于偿还公司存量有息负债。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金;本期债券募集资金将用于置换发行人前期偿还23济工01的自有资金[23济工01]</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,北京银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD87" s="3"/>
       <c r="AE87" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF87" s="3" t="inlineStr">
@@ -20074,28 +20230,28 @@
       </c>
       <c r="AG87" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>山东黄金集团有限公司2026年度第一期中期票据(品种二)</t>
+          <t>济南建工集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2056-09-18</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK87" s="3"/>
       <c r="AL87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t/>
         </is>
       </c>
       <c r="AM87" s="3" t="inlineStr">
@@ -20115,27 +20271,27 @@
       </c>
       <c r="AP87" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR87" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS87" s="3" t="inlineStr">
         <is>
-          <t>贵金属</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT87" s="3" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU87" s="3" t="inlineStr">
@@ -20160,17 +20316,15 @@
       </c>
       <c r="AY87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AZ87" s="4" t="n">
-        <v>0.02</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AZ87" s="3"/>
     </row>
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26望城经开MTN001</t>
+          <t>26镇江产投MTN007</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20180,45 +20334,49 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>102683666.IB</t>
+          <t>102683664.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>6.6</v>
+        <v>3.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>6.6</v>
+        <v>3.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>38.03</v>
+      </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>25望城经开MTN001</t>
+          <t>24镇江产投MTN004</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>3.87Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>1.8219</t>
+          <t>1.7243</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -20228,12 +20386,12 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>望城经开区投资建设集团有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>C- 19.39</t>
+          <t>C- 23.63</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20243,7 +20401,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -20257,10 +20415,10 @@
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>5.17</v>
+        <v>3.43</v>
       </c>
       <c r="V88" s="4" t="n">
-        <v>1.4</v>
+        <v>1.0</v>
       </c>
       <c r="W88" s="3" t="inlineStr">
         <is>
@@ -20269,28 +20427,28 @@
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>本次注册中期票据金额25.00亿元,本期发行规模6.60亿元,募集资金拟全部用于偿还发行人本部存量债务融资工具本金[23望城经开MTN002]</t>
+          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务。[24镇江产投MTN005]</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD88" s="3"/>
@@ -20311,7 +20469,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>望城经开区投资建设集团有限公司2026年度第一期中期票据</t>
+          <t>镇江产业投资控股集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20321,7 +20479,7 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2029-09-17</t>
         </is>
       </c>
       <c r="AK88" s="3"/>
@@ -20342,37 +20500,37 @@
       </c>
       <c r="AO88" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP88" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ88" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR88" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS88" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT88" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU88" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t/>
         </is>
       </c>
       <c r="AV88" s="3" t="inlineStr">
@@ -20382,7 +20540,7 @@
       </c>
       <c r="AW88" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX88" s="3" t="inlineStr">
@@ -20400,57 +20558,49 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26济工02</t>
+          <t>26昆仑金租绿债01</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>284042.SH</t>
-        </is>
-      </c>
+          <t>09-16 18:00</t>
+        </is>
+      </c>
+      <c r="C89" s="3"/>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2.80 ~ 3.80</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>183.97</v>
-      </c>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>24济工03</t>
+          <t>26昆仑金租债01(柜台)</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>2.8685</t>
+          <t>1.6723</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -20460,12 +20610,12 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>济南建工集团有限公司</t>
+          <t>昆仑金融租赁有限责任公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C- 16.62</t>
+          <t>B- 45.00</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20475,7 +20625,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -20492,64 +20642,68 @@
       <c r="V89" s="3"/>
       <c r="W89" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X89" s="3" t="inlineStr">
         <is>
-          <t>3.50%~3.60%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y89" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z89" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z89" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还公司债券本金;本期债券募集资金将用于置换发行人前期偿还23济工01的自有资金[23济工01]</t>
+          <t>本期绿色金融债券发行规模为人民币20亿元,募集资金全部拟投放于绿色项目。发行人建立了合格绿色项目清单,遴选两个绿色项目,拟投放金额20亿元。</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,兴业证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,招商银行股份有限公司,上海银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
       <c r="AE89" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>其他金融债</t>
         </is>
       </c>
       <c r="AF89" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG89" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>济南建工集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>昆仑金融租赁有限责任公司2026年绿色金融债券</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK89" s="3"/>
@@ -20560,7 +20714,7 @@
       </c>
       <c r="AM89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN89" s="3" t="inlineStr">
@@ -20570,32 +20724,32 @@
       </c>
       <c r="AO89" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU89" s="3" t="inlineStr">
@@ -20628,7 +20782,7 @@
     <row r="90" customHeight="true" ht="18.0">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN007</t>
+          <t>26湖北港口MTN004</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -20638,7 +20792,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>102683664.IB</t>
+          <t>102690040.IB</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -20647,36 +20801,40 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>40.03</v>
+      </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>24镇江产投MTN004</t>
+          <t>26鄂港01</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.46Y</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>1.7243</t>
+          <t>1.6479</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -20686,12 +20844,12 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>湖北港口集团有限公司</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>C- 23.63</t>
+          <t>C 26.21</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -20701,7 +20859,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 14:00</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -20715,19 +20873,19 @@
         </is>
       </c>
       <c r="U90" s="4" t="n">
-        <v>3.43</v>
+        <v>4.52</v>
       </c>
       <c r="V90" s="4" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="W90" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X90" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y90" s="3" t="inlineStr">
@@ -20738,17 +20896,17 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="AB90" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的3.00亿元中期票据全部用于偿还发行人存量有息债务。[24镇江产投MTN005]</t>
+          <t>本期中期票据发行规模为10亿元,发行人拟将募集资金用于偿还即将到期的有息债务。</t>
         </is>
       </c>
       <c r="AC90" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD90" s="3"/>
@@ -20769,7 +20927,7 @@
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第七期中期票据</t>
+          <t>湖北港口集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
@@ -20805,27 +20963,27 @@
       </c>
       <c r="AP90" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ90" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR90" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS90" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT90" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU90" s="3" t="inlineStr">
@@ -20858,7 +21016,7 @@
     <row r="91" customHeight="true" ht="18.0">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>26昆仑金租绿债01</t>
+          <t>26广核电力MTN007</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -20866,41 +21024,51 @@
           <t>09-16 18:00</t>
         </is>
       </c>
-      <c r="C91" s="3"/>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>102683660.IB</t>
+        </is>
+      </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>27.97</v>
+      </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>26昆仑金租债01(柜台)</t>
+          <t>26广核电力MTN006</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>1.6723</t>
+          <t>1.7270</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -20910,12 +21078,12 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>昆仑金融租赁有限责任公司</t>
+          <t>中国广核电力股份有限公司</t>
         </is>
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>B- 45.00</t>
+          <t>C- 15.73</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -20935,19 +21103,23 @@
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U91" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V91" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W91" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X91" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y91" s="3" t="inlineStr">
@@ -20955,30 +21127,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z91" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z91" s="3"/>
       <c r="AA91" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB91" s="3" t="inlineStr">
         <is>
-          <t>本期绿色金融债券发行规模为人民币20亿元,募集资金全部拟投放于绿色项目。发行人建立了合格绿色项目清单,遴选两个绿色项目,拟投放金额20亿元。</t>
+          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司到期贷款本息。</t>
         </is>
       </c>
       <c r="AC91" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,招商银行股份有限公司,上海银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,北京银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD91" s="3"/>
       <c r="AE91" s="3" t="inlineStr">
         <is>
-          <t>其他金融债</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF91" s="3" t="inlineStr">
@@ -20993,7 +21161,7 @@
       </c>
       <c r="AH91" s="3" t="inlineStr">
         <is>
-          <t>昆仑金融租赁有限责任公司2026年绿色金融债券</t>
+          <t>中国广核电力股份有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI91" s="3" t="inlineStr">
@@ -21003,53 +21171,53 @@
       </c>
       <c r="AJ91" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AK91" s="3"/>
       <c r="AL91" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AO91" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP91" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ91" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR91" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS91" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="AT91" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU91" s="3" t="inlineStr">
@@ -21082,7 +21250,7 @@
     <row r="92" customHeight="true" ht="18.0">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>26湖北港口MTN004</t>
+          <t>26晋能煤业MTN018</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -21092,12 +21260,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>102683671.IB</t>
+          <t>102690033.IB</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -21108,29 +21276,33 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>55.03</v>
+      </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>26鄂港01</t>
+          <t>26晋能煤业MTN015</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2.46Y</t>
+          <t>2.92Y+N</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>1.6479</t>
+          <t>1.8359</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -21140,12 +21312,12 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>湖北港口集团有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>C 26.21</t>
+          <t>B- 36.78</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21155,7 +21327,7 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>09-16 14:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -21169,19 +21341,19 @@
         </is>
       </c>
       <c r="U92" s="4" t="n">
-        <v>4.52</v>
+        <v>2.94</v>
       </c>
       <c r="V92" s="4" t="n">
-        <v>20.0</v>
+        <v>1.81</v>
       </c>
       <c r="W92" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X92" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y92" s="3" t="inlineStr">
@@ -21192,17 +21364,17 @@
       <c r="Z92" s="3"/>
       <c r="AA92" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB92" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为10亿元,发行人拟将募集资金用于偿还即将到期的有息债务。</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC92" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD92" s="3"/>
@@ -21223,7 +21395,7 @@
       </c>
       <c r="AH92" s="3" t="inlineStr">
         <is>
-          <t>湖北港口集团有限公司2026年度第四期中期票据</t>
+          <t>晋能控股煤业集团有限公司2026年度第十八期中期票据</t>
         </is>
       </c>
       <c r="AI92" s="3" t="inlineStr">
@@ -21259,27 +21431,27 @@
       </c>
       <c r="AP92" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ92" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR92" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS92" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT92" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU92" s="3" t="inlineStr">
@@ -21294,7 +21466,7 @@
       </c>
       <c r="AW92" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX92" s="3" t="inlineStr">
@@ -21312,7 +21484,7 @@
     <row r="93" customHeight="true" ht="18.0">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN007</t>
+          <t>26镇江产投MTN006</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -21322,45 +21494,49 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>102683660.IB</t>
+          <t>102683667.IB</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
+      <c r="H93" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>34.61</v>
+      </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN006</t>
+          <t>25镇江产投MTN008</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>2.02Y</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>1.7270</t>
+          <t>1.6726</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -21370,12 +21546,12 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司</t>
+          <t>镇江产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>C- 15.73</t>
+          <t>C- 23.63</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21399,19 +21575,19 @@
         </is>
       </c>
       <c r="U93" s="4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V93" s="4" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="W93" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X93" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y93" s="3" t="inlineStr">
@@ -21422,17 +21598,17 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB93" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司到期贷款本息。</t>
+          <t>发行人本次发行的1.00亿元中期票据全部用于偿还发行人存量有息债务。[24镇江产投MTN005]</t>
         </is>
       </c>
       <c r="AC93" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD93" s="3"/>
@@ -21443,7 +21619,7 @@
       </c>
       <c r="AF93" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG93" s="3" t="inlineStr">
@@ -21453,7 +21629,7 @@
       </c>
       <c r="AH93" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司2026年度第七期中期票据</t>
+          <t>镇江产业投资控股集团有限公司2026年度第六期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI93" s="3" t="inlineStr">
@@ -21463,10 +21639,14 @@
       </c>
       <c r="AJ93" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
-        </is>
-      </c>
-      <c r="AK93" s="3"/>
+          <t>2028-09-17</t>
+        </is>
+      </c>
+      <c r="AK93" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL93" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -21489,27 +21669,27 @@
       </c>
       <c r="AP93" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ93" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR93" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS93" s="3" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT93" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU93" s="3" t="inlineStr">
@@ -21542,70 +21722,70 @@
     <row r="94" customHeight="true" ht="18.0">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN018</t>
+          <t>26平安银行债01</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 17:00</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>102690033.IB</t>
+          <t>212680042.IB</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
+        <v>50.0</v>
+      </c>
+      <c r="G94" s="3"/>
+      <c r="H94" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>32.03</v>
+      </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN015</t>
+          <t>25平安银行科创债01BC</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+N</t>
+          <t>2.26Y</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>1.8359</t>
+          <t>1.5855</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/1.5200</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>平安银行股份有限公司</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>B- 36.78</t>
+          <t>A+ 84.85</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -21615,7 +21795,7 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 09:30</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr">
@@ -21625,23 +21805,19 @@
       </c>
       <c r="T94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>1.81</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
       <c r="W94" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X94" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y94" s="3" t="inlineStr">
@@ -21652,28 +21828,24 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB94" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
-        </is>
-      </c>
-      <c r="AC94" s="3" t="inlineStr">
-        <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC94" s="3"/>
       <c r="AD94" s="3"/>
       <c r="AE94" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF94" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG94" s="3" t="inlineStr">
@@ -21683,7 +21855,7 @@
       </c>
       <c r="AH94" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十八期中期票据</t>
+          <t>平安银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI94" s="3" t="inlineStr">
@@ -21693,18 +21865,18 @@
       </c>
       <c r="AJ94" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK94" s="3"/>
       <c r="AL94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN94" s="3" t="inlineStr">
@@ -21714,32 +21886,32 @@
       </c>
       <c r="AO94" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP94" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ94" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR94" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS94" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT94" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU94" s="3" t="inlineStr">
@@ -21754,7 +21926,7 @@
       </c>
       <c r="AW94" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX94" s="3" t="inlineStr">
@@ -21772,70 +21944,70 @@
     <row r="95" customHeight="true" ht="18.0">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>26镇江产投MTN006</t>
+          <t>26徽商银行债02</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 00:00</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>102683667.IB</t>
+          <t>212680051.IB</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
+        <v>100.0</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>33.03</v>
+      </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>25镇江产投MTN008</t>
+          <t>26徽商银行01</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>2.02Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>1.6726</t>
+          <t>1.5806</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/1.5800</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司</t>
+          <t>徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>C- 23.63</t>
+          <t>S- 87.48</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -21845,7 +22017,7 @@
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 00:00</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr">
@@ -21858,20 +22030,16 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U95" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V95" s="4" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
       <c r="W95" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X95" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y95" s="3" t="inlineStr">
@@ -21882,28 +22050,24 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB95" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行的1.00亿元中期票据全部用于偿还发行人存量有息债务。[24镇江产投MTN005]</t>
-        </is>
-      </c>
-      <c r="AC95" s="3" t="inlineStr">
-        <is>
-          <t>江苏江南农村商业银行股份有限公司,江苏银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和主管部门的批准用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF95" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG95" s="3" t="inlineStr">
@@ -21913,7 +22077,7 @@
       </c>
       <c r="AH95" s="3" t="inlineStr">
         <is>
-          <t>镇江产业投资控股集团有限公司2026年度第六期中期票据(浮息债券)</t>
+          <t>徽商银行股份有限公司2026年第二期金融债券</t>
         </is>
       </c>
       <c r="AI95" s="3" t="inlineStr">
@@ -21923,17 +22087,13 @@
       </c>
       <c r="AJ95" s="3" t="inlineStr">
         <is>
-          <t>2028-09-17</t>
-        </is>
-      </c>
-      <c r="AK95" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-17</t>
+        </is>
+      </c>
+      <c r="AK95" s="3"/>
       <c r="AL95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AM95" s="3" t="inlineStr">
@@ -21948,32 +22108,32 @@
       </c>
       <c r="AO95" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP95" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ95" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR95" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS95" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT95" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU95" s="3" t="inlineStr">
@@ -22006,70 +22166,74 @@
     <row r="96" customHeight="true" ht="18.0">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>26平安银行债01</t>
+          <t>26宿迁产业MTN001</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>09-16 17:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>212680042.IB</t>
+          <t>102683687.IB</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="G96" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
       <c r="H96" s="4" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>32.03</v>
+        <v>9.42</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>25平安银行科创债01BC</t>
+          <t>25产发01</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2.26Y</t>
+          <t>3.60Y+5.00Y</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>1.5855</t>
+          <t>1.6884</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>1.5800/1.5200</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司</t>
+          <t>宿迁产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>A+ 84.85</t>
+          <t>C- 12.73</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22079,7 +22243,7 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:30</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr">
@@ -22089,19 +22253,23 @@
       </c>
       <c r="T96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U96" s="4" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="V96" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W96" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X96" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y96" s="3" t="inlineStr">
@@ -22112,24 +22280,28 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB96" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC96" s="3"/>
+          <t>本期基础发行规模0亿元,发行金额上限10亿元,拟全部用于偿还发行人债务融资工具本金[23宿迁产业MTN001]</t>
+        </is>
+      </c>
+      <c r="AC96" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,江苏江南农村商业银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD96" s="3"/>
       <c r="AE96" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF96" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG96" s="3" t="inlineStr">
@@ -22139,7 +22311,7 @@
       </c>
       <c r="AH96" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司2026年金融债券(第一期)</t>
+          <t>宿迁产业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI96" s="3" t="inlineStr">
@@ -22149,20 +22321,20 @@
       </c>
       <c r="AJ96" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2036-09-17</t>
         </is>
       </c>
       <c r="AK96" s="3"/>
       <c r="AL96" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM96" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM96" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AN96" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -22170,37 +22342,37 @@
       </c>
       <c r="AO96" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP96" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ96" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR96" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>烟酒</t>
         </is>
       </c>
       <c r="AS96" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>烟酒</t>
         </is>
       </c>
       <c r="AT96" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>饮料制造</t>
         </is>
       </c>
       <c r="AU96" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AV96" s="3" t="inlineStr">
@@ -22210,7 +22382,7 @@
       </c>
       <c r="AW96" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX96" s="3" t="inlineStr">
@@ -22228,70 +22400,74 @@
     <row r="97" customHeight="true" ht="18.0">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>26徽商银行债02</t>
+          <t>26涪陵实业MTN002B</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>09-16 00:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>212680051.IB</t>
+          <t>102683683.IB</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>100.0</v>
+        <v>4.25</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="G97" s="3"/>
+        <v>4.25</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
       <c r="H97" s="4" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>33.03</v>
+        <v>87.42</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>26徽商银行01</t>
+          <t>26涪陵实业MTN001</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>6.75Y</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>1.5806</t>
+          <t>2.2223</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>1.5900/1.5800</t>
+          <t>--/2.1600</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>S- 87.48</t>
+          <t>C- 16.85</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22301,7 +22477,7 @@
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>09-16 00:00</t>
+          <t>09-16 14:00</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr">
@@ -22314,44 +22490,52 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
+      <c r="U97" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V97" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="W97" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X97" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y97" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z97" s="3"/>
       <c r="AA97" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB97" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和主管部门的批准用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC97" s="3"/>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为4.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+        </is>
+      </c>
+      <c r="AC97" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD97" s="3"/>
       <c r="AE97" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF97" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG97" s="3" t="inlineStr">
@@ -22361,7 +22545,7 @@
       </c>
       <c r="AH97" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司2026年第二期金融债券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第二期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI97" s="3" t="inlineStr">
@@ -22371,13 +22555,13 @@
       </c>
       <c r="AJ97" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2036-09-17</t>
         </is>
       </c>
       <c r="AK97" s="3"/>
       <c r="AL97" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM97" s="3" t="inlineStr">
@@ -22392,32 +22576,32 @@
       </c>
       <c r="AO97" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP97" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ97" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR97" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS97" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT97" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU97" s="3" t="inlineStr">
@@ -22450,70 +22634,72 @@
     <row r="98" customHeight="true" ht="18.0">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>26宿迁产业MTN001</t>
+          <t>26普城04</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>102683687.IB</t>
+          <t>283977.SH</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F98" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>35.97</v>
+      </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>25产发01</t>
+          <t>26普城03</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>3.60Y+5.00Y</t>
+          <t>2.62Y+2.00Y</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>1.6884</t>
+          <t>1.7316</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>1.8500/1.6900</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>宿迁产业发展集团有限公司</t>
+          <t>舟山普陀城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>C- 12.73</t>
+          <t>D+ 9.64</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -22533,50 +22719,46 @@
       </c>
       <c r="T98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
       <c r="W98" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X98" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y98" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z98" s="3"/>
       <c r="AA98" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB98" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模0亿元,发行金额上限10亿元,拟全部用于偿还发行人债务融资工具本金[23宿迁产业MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,预计全部用于偿还到期的公司债券本金[23普城04]</t>
         </is>
       </c>
       <c r="AC98" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD98" s="3"/>
       <c r="AE98" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF98" s="3" t="inlineStr">
@@ -22586,73 +22768,73 @@
       </c>
       <c r="AG98" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH98" s="3" t="inlineStr">
         <is>
-          <t>宿迁产业发展集团有限公司2026年度第一期中期票据</t>
+          <t>舟山普陀城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI98" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ98" s="3" t="inlineStr">
         <is>
-          <t>2036-09-17</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK98" s="3"/>
       <c r="AL98" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN98" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AM98" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN98" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="AO98" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP98" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ98" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR98" s="3" t="inlineStr">
         <is>
-          <t>烟酒</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS98" s="3" t="inlineStr">
         <is>
-          <t>烟酒</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT98" s="3" t="inlineStr">
         <is>
-          <t>饮料制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU98" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AV98" s="3" t="inlineStr">
@@ -22680,70 +22862,72 @@
     <row r="99" customHeight="true" ht="18.0">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002B</t>
+          <t>26昌兴01</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>102683683.IB</t>
+          <t>283986.SH</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F99" s="4" t="n">
-        <v>2.15</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F99" s="3"/>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>71.97</v>
+      </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>25昌兴02</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>6.75Y</t>
+          <t>3.56Y</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>2.2223</t>
+          <t>2.0145</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>--/2.1600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>萍乡市昌兴投资有限公司</t>
         </is>
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>C- 16.85</t>
+          <t>C 27.61</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -22753,7 +22937,7 @@
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>09-16 14:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr">
@@ -22763,50 +22947,50 @@
       </c>
       <c r="T99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U99" s="4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V99" s="4" t="n">
-        <v>4.0</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="U99" s="3"/>
+      <c r="V99" s="3"/>
       <c r="W99" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X99" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>2.10%~2.20%</t>
         </is>
       </c>
       <c r="Y99" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z99" s="3"/>
       <c r="AA99" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江西省-萍乡市</t>
         </is>
       </c>
       <c r="AB99" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为4.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期债券发行规模为不超过人民币5.00亿元(含5.00亿元),募集资金扣除发行费用后,拟全部用于偿还公司即将到期的公司债券本金[23昌兴01]</t>
         </is>
       </c>
       <c r="AC99" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD99" s="3"/>
+          <t>国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD99" s="3" t="inlineStr">
+        <is>
+          <t>江西省信用融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE99" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF99" s="3" t="inlineStr">
@@ -22816,68 +23000,68 @@
       </c>
       <c r="AG99" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH99" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第二期中期票据(品种二)</t>
+          <t>萍乡市昌兴投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI99" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ99" s="3" t="inlineStr">
         <is>
-          <t>2036-09-17</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK99" s="3"/>
       <c r="AL99" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM99" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN99" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AM99" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN99" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="AO99" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP99" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ99" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR99" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS99" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT99" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU99" s="3" t="inlineStr">
@@ -22887,7 +23071,7 @@
       </c>
       <c r="AV99" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW99" s="3" t="inlineStr">
@@ -22910,7 +23094,7 @@
     <row r="100" customHeight="true" ht="18.0">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>26普城04</t>
+          <t>26热联01</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -22920,62 +23104,62 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>283977.SH</t>
+          <t>246082.SH</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>35.97</v>
+        <v>56.03</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>26普城03</t>
+          <t>26杭州热联SCP011</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>2.62Y+2.00Y</t>
+          <t>177D</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>1.7316</t>
+          <t>1.6295</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>1.8500/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>舟山普陀城市投资发展集团有限公司</t>
+          <t>杭州热联集团股份有限公司</t>
         </is>
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.64</t>
+          <t>B- 36.38</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -23002,12 +23186,12 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X100" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y100" s="3" t="inlineStr">
@@ -23018,17 +23202,17 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB100" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,预计全部用于偿还到期的公司债券本金[23普城04]</t>
+          <t>本期公司债券募集资金拟将6.00 亿元用于偿还公司债务，2.00 亿元用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC100" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD100" s="3"/>
@@ -23049,17 +23233,17 @@
       </c>
       <c r="AH100" s="3" t="inlineStr">
         <is>
-          <t>舟山普陀城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>杭州热联集团股份有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI100" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ100" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK100" s="3"/>
@@ -23070,7 +23254,7 @@
       </c>
       <c r="AM100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN100" s="3" t="inlineStr">
@@ -23080,37 +23264,37 @@
       </c>
       <c r="AO100" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP100" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ100" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR100" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS100" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT100" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU100" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AV100" s="3" t="inlineStr">
@@ -23120,7 +23304,7 @@
       </c>
       <c r="AW100" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX100" s="3" t="inlineStr">
@@ -23138,7 +23322,7 @@
     <row r="101" customHeight="true" ht="18.0">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>26昌兴01</t>
+          <t>26苏资05</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -23148,12 +23332,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>283986.SH</t>
+          <t>246050.SH</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -23162,29 +23346,33 @@
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>32.03</v>
+      </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>25昌兴02</t>
+          <t>26苏资04</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>3.56Y</t>
+          <t>2.89Y</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>2.0145</t>
+          <t>1.7100</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -23194,12 +23382,12 @@
       </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>萍乡市昌兴投资有限公司</t>
+          <t>江苏资产管理有限公司</t>
         </is>
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>C 27.61</t>
+          <t>C 29.46</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
@@ -23209,7 +23397,7 @@
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 16:00</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr">
@@ -23226,40 +23414,36 @@
       <c r="V101" s="3"/>
       <c r="W101" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X101" s="3" t="inlineStr">
         <is>
-          <t>2.10%~2.20%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y101" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z101" s="3"/>
       <c r="AA101" s="3" t="inlineStr">
         <is>
-          <t>江西省-萍乡市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB101" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币5.00亿元(含5.00亿元),募集资金扣除发行费用后,拟全部用于偿还公司即将到期的公司债券本金[23昌兴01]</t>
+          <t>本期公司债券募集资金拟将1.895亿元用于偿还有息债务,拟将除偿还有息债务外的募集资金用于补充公司不良资产经营业务日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。</t>
         </is>
       </c>
       <c r="AC101" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD101" s="3" t="inlineStr">
-        <is>
-          <t>江西省信用融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD101" s="3"/>
       <c r="AE101" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -23277,17 +23461,17 @@
       </c>
       <c r="AH101" s="3" t="inlineStr">
         <is>
-          <t>萍乡市昌兴投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏资产管理有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI101" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ101" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK101" s="3"/>
@@ -23298,7 +23482,7 @@
       </c>
       <c r="AM101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN101" s="3" t="inlineStr">
@@ -23308,32 +23492,32 @@
       </c>
       <c r="AO101" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP101" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ101" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR101" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS101" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT101" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU101" s="3" t="inlineStr">
@@ -23343,7 +23527,7 @@
       </c>
       <c r="AV101" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW101" s="3" t="inlineStr">
@@ -23366,72 +23550,70 @@
     <row r="102" customHeight="true" ht="18.0">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>26热联01</t>
+          <t>26新业国资MTN003</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>246082.SH</t>
+          <t>102683691.IB</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F102" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I102" s="4" t="n">
-        <v>56.03</v>
-      </c>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>26杭州热联SCP011</t>
+          <t>26新业国资MTN001</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>177D</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>1.6295</t>
+          <t>2.1552</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3000/2.1000</t>
         </is>
       </c>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>杭州热联集团股份有限公司</t>
+          <t>新疆新业国有资产经营(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P102" s="3" t="inlineStr">
         <is>
-          <t>B- 36.38</t>
+          <t>C- 14.72</t>
         </is>
       </c>
       <c r="Q102" s="3" t="inlineStr">
@@ -23441,7 +23623,7 @@
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 10:00</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr">
@@ -23458,12 +23640,12 @@
       <c r="V102" s="3"/>
       <c r="W102" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X102" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y102" s="3" t="inlineStr">
@@ -23474,23 +23656,23 @@
       <c r="Z102" s="3"/>
       <c r="AA102" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AB102" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟将6.00 亿元用于偿还公司债务，2.00 亿元用于补充流动资金。</t>
+          <t>发行人本次中期票据注册金额20亿元,本期发行规模5亿元,拟全部用于偿还有息负债[23新业国资MTN002]</t>
         </is>
       </c>
       <c r="AC102" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD102" s="3"/>
       <c r="AE102" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF102" s="3" t="inlineStr">
@@ -23500,12 +23682,12 @@
       </c>
       <c r="AG102" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH102" s="3" t="inlineStr">
         <is>
-          <t>杭州热联集团股份有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>新疆新业国有资产经营(集团)有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI102" s="3" t="inlineStr">
@@ -23515,60 +23697,60 @@
       </c>
       <c r="AJ102" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK102" s="3"/>
       <c r="AL102" s="3" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AM102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AO102" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP102" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ102" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR102" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS102" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT102" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU102" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM102" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AN102" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AO102" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP102" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ102" s="3" t="inlineStr">
-        <is>
-          <t>贸易零售</t>
-        </is>
-      </c>
-      <c r="AR102" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AS102" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AT102" s="3" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="AU102" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV102" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -23586,25 +23768,27 @@
       </c>
       <c r="AY102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AZ102" s="3"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AZ102" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="103" customHeight="true" ht="18.0">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>26苏资05</t>
+          <t>26上海农商绿色债01</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>246050.SH</t>
+          <t>2621005.IB</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -23613,38 +23797,40 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F103" s="3"/>
+        <v>30.0</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H103" s="4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>32.03</v>
+        <v>30.03</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>26苏资04</t>
+          <t>25上海农商绿色债01(柜台)</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>2.89Y</t>
+          <t>1.81Y</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>1.7100</t>
+          <t>1.5011</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -23654,12 +23840,12 @@
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司</t>
+          <t>上海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>C 29.46</t>
+          <t>A 71.80</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
@@ -23669,7 +23855,7 @@
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>09-16 16:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr">
@@ -23686,12 +23872,12 @@
       <c r="V103" s="3"/>
       <c r="W103" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X103" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.51%~1.61%</t>
         </is>
       </c>
       <c r="Y103" s="3" t="inlineStr">
@@ -23699,26 +23885,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z103" s="3"/>
+      <c r="Z103" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA103" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB103" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟将1.895亿元用于偿还有息债务,拟将除偿还有息债务外的募集资金用于补充公司不良资产经营业务日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。</t>
+          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。 </t>
         </is>
       </c>
       <c r="AC103" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海浦东发展银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD103" s="3"/>
       <c r="AE103" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF103" s="3" t="inlineStr">
@@ -23728,12 +23918,12 @@
       </c>
       <c r="AG103" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH103" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
+          <t>上海农村商业银行股份有限公司2026年绿色金融债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI103" s="3" t="inlineStr">
@@ -23754,7 +23944,7 @@
       </c>
       <c r="AM103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN103" s="3" t="inlineStr">
@@ -23769,27 +23959,27 @@
       </c>
       <c r="AP103" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ103" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR103" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS103" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT103" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU103" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-16.xlsx
+++ b/data/credit_bond_all_2026-09-16.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-21" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-22" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 17.96</t>
+          <t>C- 17.77</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.80</t>
+          <t>C- 10.06</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.80</t>
+          <t>C- 10.06</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1769,7 +1769,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.53</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2221,7 +2221,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM9" s="3" t="inlineStr">
@@ -2315,7 +2315,9 @@
       <c r="E10" s="4" t="n">
         <v>8.5</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -2359,7 +2361,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 47.85</t>
+          <t>B- 39.06</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2382,7 +2384,9 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>4.22</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2921,7 +2925,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
@@ -3061,7 +3065,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 19.94</t>
+          <t>C- 17.48</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3287,7 +3291,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 24.41</t>
+          <t>C 25.63</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3517,7 +3521,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 20.27</t>
+          <t>C+ 31.14</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3747,7 +3751,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>A+ 83.50</t>
+          <t>A+ 81.95</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3969,7 +3973,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>S- 87.66</t>
+          <t>S- 89.15</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4195,7 +4199,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.99</t>
+          <t>C+ 30.59</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4435,7 +4439,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 20.27</t>
+          <t>C+ 31.14</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4669,7 +4673,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 35.76</t>
+          <t>B- 37.77</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4903,7 +4907,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.11</t>
+          <t>B- 36.38</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5137,7 +5141,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 37.55</t>
+          <t>B- 37.60</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5375,7 +5379,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 17.96</t>
+          <t>C- 17.77</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5605,7 +5609,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.42</t>
+          <t>B- 37.96</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5835,7 +5839,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.42</t>
+          <t>B- 37.96</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6067,7 +6071,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 20.55</t>
+          <t>C- 18.92</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6305,7 +6309,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 29.45</t>
+          <t>C+ 31.70</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6539,7 +6543,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 21.76</t>
+          <t>C 26.14</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6773,7 +6777,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.50</t>
+          <t>D+ 8.01</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7007,7 +7011,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 27.57</t>
+          <t>C+ 30.59</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7241,7 +7245,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B 51.55</t>
+          <t>B- 45.97</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7475,7 +7479,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.67</t>
+          <t>C+ 34.66</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7703,7 +7707,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 22.96</t>
+          <t>C- 23.36</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7937,7 +7941,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 35.76</t>
+          <t>B- 37.77</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8167,7 +8171,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B+ 55.37</t>
+          <t>B+ 55.92</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8393,7 +8397,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 42.55</t>
+          <t>B- 44.36</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8629,7 +8633,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 44.07</t>
+          <t>B- 44.80</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8855,7 +8859,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 18.84</t>
+          <t>C- 19.22</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9089,7 +9093,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 20.94</t>
+          <t>C- 22.64</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9559,7 +9563,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.51</t>
+          <t>C+ 32.63</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9793,7 +9797,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B 52.46</t>
+          <t>B+ 58.21</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -10029,7 +10033,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>B- 42.29</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10263,7 +10267,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>A- 67.59</t>
+          <t>A- 68.24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10430,7 +10434,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26皖天然气SCP002</t>
+          <t>26中化股SCP013</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10440,64 +10444,64 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>012682273.IB</t>
+          <t>012682279.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.1Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.29 ~ 1.49</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>22.06</v>
+        <v>15.65</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26皖天然气MTN001</t>
+          <t>21中化04</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>318D</t>
+          <t>74D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.5378</t>
+          <t>1.4946</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/1.5300</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>安徽省天然气开发股份有限公司</t>
+          <t>中国中化股份有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 12.11</t>
+          <t>A- 68.24</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10507,7 +10511,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-16 10:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10521,40 +10525,40 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3.6</v>
+        <v>1.0</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>1.25</v>
+        <v>1.0</v>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.58%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行2亿元超短期融资券,全部用于补充流动资金,主要为支付子公司天然气款</t>
+          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,徽商银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10565,7 +10569,7 @@
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10575,7 +10579,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>安徽省天然气开发股份有限公司2026年度第二期超短期融资券</t>
+          <t>中国中化股份有限公司2026年度第十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10585,7 +10589,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-06-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10611,27 +10615,27 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>石油化工与贸易</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10666,74 +10670,70 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP013</t>
+          <t>26民生银行债01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 17:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>012682279.IB</t>
+          <t>212680044.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>20.0</v>
+        <v>100.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>1.29 ~ 1.49</t>
-        </is>
-      </c>
+        <v>100.0</v>
+      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="4" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>15.65</v>
+        <v>33.03</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21中化04</t>
+          <t>25民生银行债02</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>74D</t>
+          <t>2.22Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.4946</t>
+          <t>1.5940</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>A- 67.59</t>
+          <t>S- 86.16</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 09:30</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10756,12 +10756,8 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U46" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -10769,7 +10765,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10785,23 +10781,19 @@
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
-        </is>
-      </c>
-      <c r="AC46" s="3" t="inlineStr">
-        <is>
-          <t>渤海银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10811,7 +10803,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第十三期超短期融资券</t>
+          <t>中国民生银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10821,7 +10813,7 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2029-09-17</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10832,7 +10824,7 @@
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
@@ -10842,32 +10834,32 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>石油化工与贸易</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10895,77 +10887,71 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ46" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ46" s="3"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26民生银行债01</t>
+          <t>26金随01</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>09-16 17:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>212680044.IB</t>
+          <t>283835.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="G47" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 3.00</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>33.03</v>
+        <v>64.97</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>25民生银行债02</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>2.22Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.5940</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>湖北金随矿业发展有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>A+ 82.26</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10975,7 +10961,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:30</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10988,75 +10974,81 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4" t="n">
+        <v>3.78</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X47" s="3" t="inlineStr">
-        <is>
-          <t>1.57%~1.67%</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X47" s="3"/>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-随州市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过1.60亿元用于支付两项饰面用花岗岩矿采矿权出让费用;拟将不超过3.40亿元用于偿还有息负债,募集资金规模共计不超过5.00亿元。</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>东方证券股份有限公司,东北证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr">
+        <is>
+          <t>湖北省融资担保集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司2026年金融债券(第一期)</t>
+          <t>湖北金随矿业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
@@ -11066,32 +11058,28 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP47" s="3"/>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>其他矿产</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>其他矿产</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>其他采掘</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -11101,7 +11089,7 @@
       </c>
       <c r="AV47" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW47" s="3" t="inlineStr">
@@ -11124,17 +11112,17 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26金随01</t>
+          <t>26南通城建MTN003</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>283835.SH</t>
+          <t>102683684.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -11143,108 +11131,118 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>64.97</v>
+        <v>35.97</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>26南通城建MTN002</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>4.90Y</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1.7881</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>1.7800/--</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>南通城市建设集团有限公司</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>B- 44.05</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>09-16 14:00</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>湖北金随矿业发展有限公司</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>09-16 15:00</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
       <c r="U48" s="4" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V48" s="3"/>
+        <v>6.85</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>6.47</v>
+      </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X48" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>湖北省-随州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过1.60亿元用于支付两项饰面用花岗岩矿采矿权出让费用;拟将不超过3.40亿元用于偿还有息负债,募集资金规模共计不超过5.00亿元。</t>
+          <t>发行人本次中期票据注册金额为35.00亿元,本期发行10.00亿元,募集资金用于偿还发行人有息债务。[26南通城建SCP004]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,东北证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="inlineStr">
-        <is>
-          <t>湖北省融资担保集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中国光大银行股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11254,17 +11252,17 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>湖北金随矿业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南通城市建设集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
@@ -11275,53 +11273,57 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AO48" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP48" s="3"/>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>其他矿产</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>其他矿产</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>其他采掘</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW48" s="3" t="inlineStr">
@@ -11339,12 +11341,14 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ48" s="3"/>
+      <c r="AZ48" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN003</t>
+          <t>26中兴通讯SCP038</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -11354,64 +11358,64 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>102683684.IB</t>
+          <t>012682274.IB</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.29Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.25 ~ 1.65</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>35.97</v>
+        <v>15.71</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN002</t>
+          <t>26中兴通讯MTN001</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>2.41Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.7881</t>
+          <t>1.7064</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>1.7800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>中兴通讯股份有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>B- 41.35</t>
+          <t>C+ 32.63</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11421,7 +11425,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>09-16 14:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -11435,19 +11439,19 @@
         </is>
       </c>
       <c r="U49" s="4" t="n">
-        <v>6.85</v>
+        <v>2.1</v>
       </c>
       <c r="V49" s="4" t="n">
-        <v>6.47</v>
+        <v>1.0</v>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -11458,28 +11462,28 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据注册金额为35.00亿元,本期发行10.00亿元,募集资金用于偿还发行人有息债务。[26南通城建SCP004]</t>
+          <t>本期超短期融资券拟募集资金6亿元，资金将全部用于偿还发行人即将到期的债务融资工具本息。[26中兴通讯SCP026]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,南京银行股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG49" s="3" t="inlineStr">
@@ -11489,7 +11493,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第三期中期票据</t>
+          <t>中兴通讯股份有限公司2026年度第三十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11499,7 +11503,7 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
@@ -11520,32 +11524,32 @@
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子设备制造</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11574,13 +11578,13 @@
         </is>
       </c>
       <c r="AZ49" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26中兴通讯SCP038</t>
+          <t>26浙商资产SCP003</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11590,64 +11594,64 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>012682274.IB</t>
+          <t>012682275.IB</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0.29Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.65</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>15.71</v>
+        <v>20.06</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>26中兴通讯MTN001</t>
+          <t>24浙商G2</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2.41Y</t>
+          <t>243D+2.00Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.7064</t>
+          <t>1.5711</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5600/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>中兴通讯股份有限公司</t>
+          <t>浙江省浙商资产管理股份有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.51</t>
+          <t>C- 23.56</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11657,7 +11661,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 10:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11671,19 +11675,19 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>2.1</v>
+        <v>4.48</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.53%~1.57%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11694,17 +11698,17 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金6亿元，资金将全部用于偿还发行人即将到期的债务融资工具本息。[26中兴通讯SCP026]</t>
+          <t>发行人本期超短期融资券发行规模5.00亿元，拟用于偿还发行人到期的债务融资工具本金[23浙商资产MTN006]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
@@ -11715,7 +11719,7 @@
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
@@ -11725,7 +11729,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>中兴通讯股份有限公司2026年度第三十八期超短期融资券</t>
+          <t>浙江省浙商资产管理股份有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11735,10 +11739,14 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="AK50" s="3"/>
+          <t>2027-06-09</t>
+        </is>
+      </c>
+      <c r="AK50" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL50" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -11756,32 +11764,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11809,14 +11817,12 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ50" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ50" s="3"/>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26浙商资产SCP003</t>
+          <t>26鲁高速SCP002</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11826,64 +11832,64 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>012682275.IB</t>
+          <t>012682276.IB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>20.06</v>
+        <v>14.0</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>24浙商G2</t>
+          <t>23鲁高K2</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>243D+2.00Y</t>
+          <t>58D+2.00Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.5711</t>
+          <t>1.4664</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1.5600/--</t>
+          <t>1.4800/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>浙江省浙商资产管理股份有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 22.38</t>
+          <t>B- 41.83</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11907,19 +11913,17 @@
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="V51" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>1.452</v>
+      </c>
+      <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
@@ -11930,17 +11934,17 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模5.00亿元，拟用于偿还发行人到期的债务融资工具本金[23浙商资产MTN006]</t>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限25亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金。</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
@@ -11961,7 +11965,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>浙江省浙商资产管理股份有限公司2026年度第三期超短期融资券</t>
+          <t>山东高速集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11971,14 +11975,10 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2027-06-09</t>
-        </is>
-      </c>
-      <c r="AK51" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="AK51" s="3"/>
       <c r="AL51" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP51" s="3" t="inlineStr">
@@ -12006,22 +12006,22 @@
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -12049,12 +12049,14 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ51" s="3"/>
+      <c r="AZ51" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP002</t>
+          <t>26中飞租赁MTN001</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -12064,64 +12066,64 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>012682276.IB</t>
+          <t>102683672.IB</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>14.0</v>
+        <v>51.61</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>23鲁高K2</t>
+          <t>25中飞租赁MTN002</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>58D+2.00Y</t>
+          <t>1.24Y+N</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.4664</t>
+          <t>1.7289</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>1.4800/--</t>
+          <t>1.9000/--</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>中飞租融资租赁有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 39.29</t>
+          <t>B- 36.94</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12131,7 +12133,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>09-16 10:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -12145,17 +12147,19 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>1.452</v>
-      </c>
-      <c r="V52" s="3"/>
+        <v>2.98</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>1.45</v>
+      </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -12166,28 +12170,28 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限25亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金。</t>
+          <t>本期债券募集资金用于归还发行人的待偿还公司债务[24中飞租赁MTN002]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司,渤海银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr">
@@ -12197,7 +12201,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第二期超短期融资券</t>
+          <t>中飞租融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12207,10 +12211,14 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="AK52" s="3"/>
+          <t>2028-09-17</t>
+        </is>
+      </c>
+      <c r="AK52" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL52" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -12228,32 +12236,32 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12268,12 +12276,12 @@
       </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX52" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY52" s="3" t="inlineStr">
@@ -12282,28 +12290,28 @@
         </is>
       </c>
       <c r="AZ52" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26中飞租赁MTN001</t>
+          <t>26浙能源SCP004</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 17:00</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>102683672.IB</t>
+          <t>012682283.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -12314,48 +12322,48 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 1.55</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>51.61</v>
+        <v>14.26</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>25中飞租赁MTN002</t>
+          <t>24浙能源MTN003</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>1.24Y+N</t>
+          <t>332D</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.7289</t>
+          <t>1.5188</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1.9000/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>中飞租融资租赁有限公司</t>
+          <t>浙江省能源集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>B- 39.88</t>
+          <t>C 28.80</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12365,7 +12373,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -12379,19 +12387,19 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>2.98</v>
+        <v>1.79</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>1.45</v>
+        <v>1.0</v>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -12402,28 +12410,28 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金用于归还发行人的待偿还公司债务[24中飞租赁MTN002]</t>
+          <t>发行人本次拟发行10亿元，其中用于偿还到期的债务融资工具10亿元[26浙能源SCP002（科创债）]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
@@ -12433,7 +12441,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>中飞租融资租赁有限公司2026年度第一期中期票据</t>
+          <t>浙江省能源集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12443,14 +12451,10 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2028-09-17</t>
-        </is>
-      </c>
-      <c r="AK53" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-04-15</t>
+        </is>
+      </c>
+      <c r="AK53" s="3"/>
       <c r="AL53" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -12468,32 +12472,32 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -12508,12 +12512,12 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY53" s="3" t="inlineStr">
@@ -12521,81 +12525,79 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ53" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ53" s="3"/>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26浙能源SCP004</t>
+          <t>26涪陵实业MTN002B</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>09-16 17:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>012682283.IB</t>
+          <t>102683683.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>10.0</v>
+        <v>4.25</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.0</v>
+        <v>4.25</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.55</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.35</v>
+        <v>2.56</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>14.26</v>
+        <v>87.42</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>24浙能源MTN003</t>
+          <t>26涪陵实业MTN001</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>332D</t>
+          <t>6.75Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.5188</t>
+          <t>2.2223</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/2.1600</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>浙江省能源集团有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C 28.30</t>
+          <t>C- 22.98</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12605,7 +12607,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 14:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -12619,46 +12621,46 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>1.79</v>
+        <v>2.3765</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行10亿元，其中用于偿还到期的债务融资工具10亿元[26浙能源SCP002（科创债）]</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为4.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF54" s="3" t="inlineStr">
@@ -12673,7 +12675,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>浙江省能源集团有限公司2026年度第四期超短期融资券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第二期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12683,7 +12685,7 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2027-04-15</t>
+          <t>2036-09-17</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
@@ -12704,32 +12706,32 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12762,74 +12764,74 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002B</t>
+          <t>26苏资05</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>102683683.IB</t>
+          <t>246050.SH</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.25</v>
+        <v>5.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4.25</v>
+        <v>5.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>2.56</v>
+        <v>1.57</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>87.42</v>
+        <v>32.03</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>26苏资04</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>6.75Y</t>
+          <t>2.89Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>2.2223</t>
+          <t>1.7100</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/2.1600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>江苏资产管理有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C- 24.07</t>
+          <t>C- 24.94</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12839,7 +12841,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>09-16 14:00</t>
+          <t>09-16 16:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12849,50 +12851,48 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="V55" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>3.42</v>
+      </c>
+      <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为4.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期公司债券募集资金拟将1.895亿元用于偿还有息债务,拟将除偿还有息债务外的募集资金用于补充公司不良资产经营业务日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第二期中期票据(品种二)</t>
+          <t>江苏资产管理有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12917,53 +12917,53 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2036-09-17</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AM55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -12996,74 +12996,74 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26苏资05</t>
+          <t>26宿迁产业MTN001</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>246050.SH</t>
+          <t>102683687.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>32.03</v>
+        <v>9.42</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26苏资04</t>
+          <t>25产发01</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2.89Y</t>
+          <t>3.60Y+5.00Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.7100</t>
+          <t>1.6884</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司</t>
+          <t>宿迁产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C 26.87</t>
+          <t>C- 18.70</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>09-16 16:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -13083,21 +13083,23 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V56" s="3"/>
+        <v>5.38</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -13108,23 +13110,23 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟将1.895亿元用于偿还有息债务,拟将除偿还有息债务外的募集资金用于补充公司不良资产经营业务日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。</t>
+          <t>本期基础发行规模0亿元,发行金额上限10亿元,拟全部用于偿还发行人债务融资工具本金[23宿迁产业MTN001]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
@@ -13134,12 +13136,12 @@
       </c>
       <c r="AG56" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
+          <t>宿迁产业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -13149,28 +13151,28 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2036-09-17</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
@@ -13180,27 +13182,27 @@
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>烟酒</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>烟酒</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>饮料制造</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AV56" s="3" t="inlineStr">
@@ -13210,7 +13212,7 @@
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX56" s="3" t="inlineStr">
@@ -13228,74 +13230,74 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26宿迁产业MTN001</t>
+          <t>26昌洋01</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>102683687.IB</t>
+          <t>284030.SH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9.42</v>
+        <v>88.97</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>25产发01</t>
+          <t>25昌洋01</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>3.60Y+5.00Y</t>
+          <t>4.14Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.6884</t>
+          <t>2.1705</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>--/2.1000</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>宿迁产业发展集团有限公司</t>
+          <t>威海市昌洋实业有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 20.33</t>
+          <t>D+ 6.15</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13315,50 +13317,52 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="V57" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>3.95</v>
+      </c>
+      <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.43%~2.53%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模0亿元,发行金额上限10亿元,拟全部用于偿还发行人债务融资工具本金[23宿迁产业MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,江苏江南农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD57" s="3"/>
+          <t>中泰证券股份有限公司,甬兴证券有限公司,德邦证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr">
+        <is>
+          <t>青岛增信融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -13368,83 +13372,83 @@
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>宿迁产业发展集团有限公司2026年度第一期中期票据</t>
+          <t>威海市昌洋实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2036-09-17</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AM57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>烟酒</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>烟酒</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>饮料制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t/>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
@@ -13462,74 +13466,74 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26昌洋01</t>
+          <t>26昆仑金租绿色债</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>284030.SH</t>
+          <t>2622019.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>88.97</v>
+        <v>35.03</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>25昌洋01</t>
+          <t>26昆仑金租债01(柜台)</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>4.14Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2.1705</t>
+          <t>1.6723</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/2.1000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>威海市昌洋实业有限公司</t>
+          <t>昆仑金融租赁有限责任公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.15</t>
+          <t>B 53.75</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13539,7 +13543,7 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 09:00</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -13552,130 +13556,128 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U58" s="4" t="n">
-        <v>3.95</v>
-      </c>
+      <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>2.43%~2.53%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z58" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务</t>
+          <t>本期绿色金融债券发行规模为人民币20亿元,募集资金全部拟投放于绿色项目。发行人建立了合格绿色项目清单,遴选两个绿色项目,拟投放金额20亿元。</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,甬兴证券有限公司,德邦证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD58" s="3" t="inlineStr">
-        <is>
-          <t>青岛增信融资担保有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,招商银行股份有限公司,上海银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,北京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>其他金融债</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>威海市昌洋实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
+          <t>昆仑金融租赁有限责任公司2026年绿色金融债券</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>金融租赁</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>金融租赁</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AO58" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ58" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR58" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS58" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT58" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU58" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV58" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW58" s="3" t="inlineStr">
@@ -13698,7 +13700,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26昆仑金租绿色债</t>
+          <t>26苏交通CP007</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13708,12 +13710,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>2622019.IB</t>
+          <t>042680318.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
@@ -13724,33 +13726,33 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>35.03</v>
+        <v>17.98</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26昆仑金租债01(柜台)</t>
+          <t>22苏交通MTN006</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>364D</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.6723</t>
+          <t>1.5207</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -13760,12 +13762,12 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>昆仑金融租赁有限责任公司</t>
+          <t>江苏交通控股有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>B- 46.89</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13785,19 +13787,23 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>1.36</v>
+      </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13805,35 +13811,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z59" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期绿色金融债券发行规模为人民币20亿元,募集资金全部拟投放于绿色项目。发行人建立了合格绿色项目清单,遴选两个绿色项目,拟投放金额20亿元。</t>
+          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,招商银行股份有限公司,上海银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,北京银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>其他金融债</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13843,7 +13845,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>昆仑金融租赁有限责任公司2026年绿色金融债券</t>
+          <t>江苏交通控股有限公司2026年度第七期短期融资券</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13853,53 +13855,53 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13932,7 +13934,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP007</t>
+          <t>26上海农商绿色债02</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13942,30 +13944,30 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>042680318.IB</t>
+          <t>2621006.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.35 ~ 1.85</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17.98</v>
+        <v>35.03</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -13974,17 +13976,17 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>22苏交通MTN006</t>
+          <t>25上海农商绿色债01(柜台)</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>364D</t>
+          <t>1.81Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.5207</t>
+          <t>1.5011</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -13994,12 +13996,12 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司</t>
+          <t>上海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>B- 49.11</t>
+          <t>B+ 56.03</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14019,23 +14021,19 @@
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="n">
-        <v>2.755</v>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>1.36</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.51%~1.61%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -14043,26 +14041,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z60" s="3"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
+          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。 </t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中信银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海浦东发展银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
@@ -14077,7 +14079,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司2026年度第七期短期融资券</t>
+          <t>上海农村商业银行股份有限公司2026年绿色金融债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14087,53 +14089,53 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AM60" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14166,22 +14168,22 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26上海农商绿色债02</t>
+          <t>26中交天航MTN002</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>2621006.IB</t>
+          <t>102683690.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -14192,33 +14194,33 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.85</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>35.03</v>
+        <v>57.21</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>25上海农商绿色债01(柜台)</t>
+          <t>26中交天航MTN001</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>1.81Y</t>
+          <t>2.71Y+N</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.5011</t>
+          <t>1.7673</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -14228,12 +14230,12 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司</t>
+          <t>中交天津航道局有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>A- 65.86</t>
+          <t>C- 22.41</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14256,52 +14258,54 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U61" s="3"/>
+      <c r="U61" s="4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.61%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。 </t>
+          <t>发行人本期中期票据拟发行10亿元,归还发行人本部存量有息债务[23中交天航MTN002(科创票据)]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海浦东发展银行股份有限公司,华夏银行股份有限公司</t>
+          <t>招商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
@@ -14311,7 +14315,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司2026年绿色金融债券(第一期)(品种二)</t>
+          <t>中交天津航道局有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14332,7 +14336,7 @@
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
@@ -14342,32 +14346,32 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -14382,17 +14386,17 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AZ61" s="3"/>
@@ -14400,59 +14404,59 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26中交天航MTN002</t>
+          <t>26海尔03</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>102683690.IB</t>
+          <t>246060.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>57.21</v>
+        <v>50.61</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26中交天航MTN001</t>
+          <t>26海尔02</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.71Y+N</t>
+          <t>265D+1.00Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7673</t>
+          <t>1.7713</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -14462,12 +14466,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>中交天津航道局有限公司</t>
+          <t>海尔融资租赁股份有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.40</t>
+          <t>D+ 6.53</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14477,7 +14481,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>09-16 09:00</t>
+          <t>09-16 15:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -14487,67 +14491,63 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.67%~1.71%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z62" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟发行10亿元,归还发行人本部存量有息债务[23中交天航MTN002(科创票据)]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将用于偿还公司债券本金及补充流动资金[G25 海尔D]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,渤海银行股份有限公司</t>
+          <t>平安证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>中交天津航道局有限公司2026年度第二期中期票据</t>
+          <t>海尔融资租赁股份有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14557,58 +14557,62 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
-        </is>
-      </c>
-      <c r="AK62" s="3"/>
+          <t>2028-09-17</t>
+        </is>
+      </c>
+      <c r="AK62" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AM62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="AV62" s="3" t="inlineStr">
@@ -14618,17 +14622,17 @@
       </c>
       <c r="AW62" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX62" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AZ62" s="3"/>
@@ -14636,7 +14640,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26海尔03</t>
+          <t>26华租01</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14646,12 +14650,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>246060.SH</t>
+          <t>246059.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
@@ -14662,48 +14666,48 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.25 ~ 2.25</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>50.61</v>
+        <v>43.03</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26海尔02</t>
+          <t>G26华租1</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>265D+1.00Y</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.7713</t>
+          <t>1.7419</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>海尔融资租赁股份有限公司</t>
+          <t>华电融资租赁有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.55</t>
+          <t>C 25.48</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14727,17 +14731,17 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>1.57</v>
+        <v>5.44</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.71%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -14745,20 +14749,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z63" s="3"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将用于偿还公司债券本金及补充流动资金[G25 海尔D]</t>
+          <t>本期债券发行金额为不超过5亿元(含5亿元),扣除发行费用后,募集资金拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,东方证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,光大证券股份有限公司,国新证券股份有限公司,川财证券有限责任公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
@@ -14769,7 +14777,7 @@
       </c>
       <c r="AF63" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG63" s="3" t="inlineStr">
@@ -14779,7 +14787,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>海尔融资租赁股份有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>华电融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14789,14 +14797,10 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2028-09-17</t>
-        </is>
-      </c>
-      <c r="AK63" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-17</t>
+        </is>
+      </c>
+      <c r="AK63" s="3"/>
       <c r="AL63" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -14819,7 +14823,7 @@
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
@@ -14844,7 +14848,7 @@
       </c>
       <c r="AU63" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t/>
         </is>
       </c>
       <c r="AV63" s="3" t="inlineStr">
@@ -14854,7 +14858,7 @@
       </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX63" s="3" t="inlineStr">
@@ -14872,7 +14876,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26华租01</t>
+          <t>26菏投F1</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14882,49 +14886,49 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>246059.SH</t>
+          <t>284038.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>5.0</v>
+        <v>1.7</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>5.0</v>
+        <v>1.7</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 2.25</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>43.03</v>
+        <v>68.97</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>G26华租1</t>
+          <t>25菏投05</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>4.04Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.7419</t>
+          <t>2.1656</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -14934,12 +14938,12 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>华电融资租赁有限公司</t>
+          <t>山东菏建国有资本投资有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C- 23.15</t>
+          <t>C- 16.56</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14963,42 +14967,38 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>5.44</v>
+        <v>3.76</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z64" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过5亿元(含5亿元),扣除发行费用后,募集资金拟全部用于偿还有息债务</t>
+          <t>本期债券募集资金不超过1.70亿元(含1.70亿元)拟全部用于偿还到期/回售的公司债券本金[21菏投02]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,光大证券股份有限公司,国新证券股份有限公司,川财证券有限责任公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -15019,17 +15019,17 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>华电融资租赁有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>山东菏建国有资本投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2029-09-17</t>
+          <t>2031-09-17</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="AM64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN64" s="3" t="inlineStr">
@@ -15050,32 +15050,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15108,74 +15108,74 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26菏投F1</t>
+          <t>26皖天然气SCP002</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>284038.SH</t>
+          <t>012682273.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.7</v>
+        <v>2.0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.7</v>
+        <v>2.0</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>68.97</v>
+        <v>22.06</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>25菏投05</t>
+          <t>26皖天然气MTN001</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>4.04Y</t>
+          <t>318D</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>2.1656</t>
+          <t>1.5378</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5300</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>山东菏建国有资本投资有限公司</t>
+          <t>安徽省天然气开发股份有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C- 16.56</t>
+          <t>C- 17.67</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>09-16 15:00</t>
+          <t>09-16 10:00</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -15199,17 +15199,19 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="V65" s="3"/>
+        <v>3.6</v>
+      </c>
+      <c r="V65" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>1.54%~1.58%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -15220,23 +15222,23 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过1.70亿元(含1.70亿元)拟全部用于偿还到期/回售的公司债券本金[21菏投02]</t>
+          <t>发行人本次发行2亿元超短期融资券,全部用于补充流动资金,主要为支付子公司天然气款</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
+          <t>兴业银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -15246,28 +15248,28 @@
       </c>
       <c r="AG65" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>山东菏建国有资本投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>安徽省天然气开发股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
+          <t>2027-06-14</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM65" s="3" t="inlineStr">
@@ -15282,32 +15284,32 @@
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -15335,7 +15337,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AZ65" s="3"/>
+      <c r="AZ65" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
@@ -15407,7 +15411,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.58</t>
+          <t>C+ 34.34</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15635,7 +15639,7 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C- 24.07</t>
+          <t>C- 22.98</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15869,7 +15873,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>C- 19.08</t>
+          <t>C- 23.62</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -16203,7 +16207,7 @@
       <c r="AK69" s="3"/>
       <c r="AL69" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM69" s="3" t="inlineStr">
@@ -16343,7 +16347,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C 26.72</t>
+          <t>C 25.42</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16811,7 +16815,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.51</t>
+          <t>C+ 32.63</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -17045,7 +17049,7 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C- 15.92</t>
+          <t>C- 17.05</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17279,7 +17283,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B- 39.69</t>
+          <t>B- 38.24</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17513,7 +17517,7 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>B- 39.83</t>
+          <t>B- 38.74</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17747,7 +17751,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C- 22.96</t>
+          <t>C- 23.36</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17985,7 +17989,7 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>B 53.75</t>
+          <t>A 70.78</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18213,7 +18217,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C- 19.25</t>
+          <t>C- 21.83</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18445,7 +18449,7 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C 25.63</t>
+          <t>C+ 31.61</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18677,7 +18681,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>B- 47.38</t>
+          <t>B- 46.49</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18913,7 +18917,7 @@
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C 27.58</t>
+          <t>C 25.52</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -19009,7 +19013,7 @@
       <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM81" s="3" t="inlineStr">
@@ -19241,7 +19245,7 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM82" s="3" t="inlineStr">
@@ -19381,7 +19385,7 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>C- 10.24</t>
+          <t>C- 12.22</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19613,7 +19617,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>B- 35.04</t>
+          <t>B- 35.49</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19709,7 +19713,7 @@
       <c r="AK84" s="3"/>
       <c r="AL84" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM84" s="3" t="inlineStr">
@@ -19849,7 +19853,7 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>B- 35.04</t>
+          <t>B- 35.49</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19945,7 +19949,7 @@
       <c r="AK85" s="3"/>
       <c r="AL85" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM85" s="3" t="inlineStr">
@@ -20085,7 +20089,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.50</t>
+          <t>B- 35.02</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20175,7 +20179,7 @@
       <c r="AK86" s="3"/>
       <c r="AL86" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM86" s="3" t="inlineStr">
@@ -20315,7 +20319,7 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C 26.14</t>
+          <t>C 26.47</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20407,7 +20411,7 @@
       <c r="AK87" s="3"/>
       <c r="AL87" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM87" s="3" t="inlineStr">
@@ -20547,7 +20551,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.16</t>
+          <t>C- 12.78</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20639,7 +20643,7 @@
       <c r="AK88" s="3"/>
       <c r="AL88" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM88" s="3" t="inlineStr">
@@ -20779,7 +20783,7 @@
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.80</t>
+          <t>D+ 6.55</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20871,7 +20875,7 @@
       <c r="AK89" s="3"/>
       <c r="AL89" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM89" s="3" t="inlineStr">
@@ -21011,7 +21015,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>C- 19.77</t>
+          <t>C- 15.93</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21103,7 +21107,7 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM90" s="3" t="inlineStr">
@@ -21335,7 +21339,7 @@
       <c r="AK91" s="3"/>
       <c r="AL91" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM91" s="3" t="inlineStr">
@@ -21475,7 +21479,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.53</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21707,7 +21711,7 @@
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>C- 23.94</t>
+          <t>C 29.50</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21799,7 +21803,7 @@
       <c r="AK93" s="3"/>
       <c r="AL93" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM93" s="3" t="inlineStr">
@@ -21939,7 +21943,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.58</t>
+          <t>C+ 34.34</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -22173,7 +22177,7 @@
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>C- 24.41</t>
+          <t>C 25.63</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22405,7 +22409,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>A 73.85</t>
+          <t>S- 85.86</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22641,7 +22645,7 @@
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>A- 65.86</t>
+          <t>B+ 56.03</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22875,7 +22879,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>B- 42.29</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -23353,7 +23357,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>C- 12.46</t>
+          <t>C- 16.44</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -23589,7 +23593,7 @@
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>C- 19.08</t>
+          <t>C- 23.62</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
@@ -23827,7 +23831,7 @@
       </c>
       <c r="P102" s="3" t="inlineStr">
         <is>
-          <t>C- 24.19</t>
+          <t>C 26.22</t>
         </is>
       </c>
       <c r="Q102" s="3" t="inlineStr">
@@ -24049,7 +24053,7 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -24059,7 +24063,7 @@
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>B- 39.40</t>
+          <t>B- 43.63</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
